--- a/1. Reporting_Data/IB_Daily Ticker/processed/2026/202610/Ticker_20261007.xlsx
+++ b/1. Reporting_Data/IB_Daily Ticker/processed/2026/202610/Ticker_20261007.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="309">
   <si>
     <t>Symbol</t>
   </si>
@@ -34,6 +34,60 @@
     <t>BloombergIdentifier</t>
   </si>
   <si>
+    <t>000660.KS</t>
+  </si>
+  <si>
+    <t>000880.KS</t>
+  </si>
+  <si>
+    <t>001720.KS</t>
+  </si>
+  <si>
+    <t>004170.KS</t>
+  </si>
+  <si>
+    <t>005930.KS</t>
+  </si>
+  <si>
+    <t>009150.KS</t>
+  </si>
+  <si>
+    <t>010120.KS</t>
+  </si>
+  <si>
+    <t>010950.KS</t>
+  </si>
+  <si>
+    <t>011070.KS</t>
+  </si>
+  <si>
+    <t>011200</t>
+  </si>
+  <si>
+    <t>016Z</t>
+  </si>
+  <si>
+    <t>018260.KS</t>
+  </si>
+  <si>
+    <t>026960.KS</t>
+  </si>
+  <si>
+    <t>071050</t>
+  </si>
+  <si>
+    <t>078930.KS</t>
+  </si>
+  <si>
+    <t>086280</t>
+  </si>
+  <si>
+    <t>096770.KS</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
     <t>1109</t>
   </si>
   <si>
@@ -52,21 +106,42 @@
     <t>1810</t>
   </si>
   <si>
+    <t>2303</t>
+  </si>
+  <si>
     <t>2359</t>
   </si>
   <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
     <t>2800</t>
   </si>
   <si>
     <t>2828</t>
   </si>
   <si>
+    <t>2892</t>
+  </si>
+  <si>
     <t>2899</t>
   </si>
   <si>
     <t>3067</t>
   </si>
   <si>
+    <t>316140.KS</t>
+  </si>
+  <si>
+    <t>3328</t>
+  </si>
+  <si>
+    <t>3711</t>
+  </si>
+  <si>
     <t>3750</t>
   </si>
   <si>
@@ -76,6 +151,9 @@
     <t>3988</t>
   </si>
   <si>
+    <t>4062.T</t>
+  </si>
+  <si>
     <t>6301.T</t>
   </si>
   <si>
@@ -85,15 +163,30 @@
     <t>700</t>
   </si>
   <si>
+    <t>836</t>
+  </si>
+  <si>
     <t>8360.T</t>
   </si>
   <si>
     <t>9633</t>
   </si>
   <si>
+    <t>992</t>
+  </si>
+  <si>
     <t>A17U</t>
   </si>
   <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
     <t>AVDV</t>
   </si>
   <si>
@@ -145,12 +238,18 @@
     <t>D05</t>
   </si>
   <si>
+    <t>DB1</t>
+  </si>
+  <si>
     <t>DBMF</t>
   </si>
   <si>
     <t>DDOG</t>
   </si>
   <si>
+    <t>DELL</t>
+  </si>
+  <si>
     <t>DG</t>
   </si>
   <si>
@@ -166,6 +265,9 @@
     <t>EWY</t>
   </si>
   <si>
+    <t>G1A</t>
+  </si>
+  <si>
     <t>GEV</t>
   </si>
   <si>
@@ -181,6 +283,12 @@
     <t>ICE</t>
   </si>
   <si>
+    <t>IGV</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
     <t>IQQ</t>
   </si>
   <si>
@@ -193,21 +301,42 @@
     <t>KMLM</t>
   </si>
   <si>
+    <t>KNIN</t>
+  </si>
+  <si>
     <t>KORU</t>
   </si>
   <si>
     <t>LAC</t>
   </si>
   <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
     <t>LLY</t>
   </si>
   <si>
+    <t>MAR</t>
+  </si>
+  <si>
     <t>MCD</t>
   </si>
   <si>
     <t>ME8U</t>
   </si>
   <si>
+    <t>MRK</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
     <t>NVO</t>
   </si>
   <si>
@@ -220,12 +349,18 @@
     <t>PKB</t>
   </si>
   <si>
+    <t>QIA</t>
+  </si>
+  <si>
     <t>QQQ</t>
   </si>
   <si>
     <t>QQQM</t>
   </si>
   <si>
+    <t>S63</t>
+  </si>
+  <si>
     <t>S68</t>
   </si>
   <si>
@@ -235,6 +370,9 @@
     <t>SCJ</t>
   </si>
   <si>
+    <t>SHELl</t>
+  </si>
+  <si>
     <t>SHLD</t>
   </si>
   <si>
@@ -247,6 +385,9 @@
     <t>SMH</t>
   </si>
   <si>
+    <t>SOON</t>
+  </si>
+  <si>
     <t>SOXX</t>
   </si>
   <si>
@@ -256,15 +397,30 @@
     <t>SPXL</t>
   </si>
   <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
     <t>TQQQ</t>
   </si>
   <si>
+    <t>TSEM</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
     <t>U11</t>
   </si>
   <si>
     <t>U96</t>
   </si>
   <si>
+    <t>UAE</t>
+  </si>
+  <si>
     <t>USMV</t>
   </si>
   <si>
@@ -286,12 +442,27 @@
     <t>VZ</t>
   </si>
   <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>XLK</t>
+  </si>
+  <si>
     <t>XLV</t>
   </si>
   <si>
+    <t>XRO</t>
+  </si>
+  <si>
     <t>Z74</t>
   </si>
   <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -304,9 +475,24 @@
     <t>USD</t>
   </si>
   <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
     <t>STK</t>
   </si>
   <si>
+    <t>FUT</t>
+  </si>
+  <si>
     <t>COMMON</t>
   </si>
   <si>
@@ -328,12 +514,66 @@
     <t>Equity</t>
   </si>
   <si>
+    <t>Derivatives</t>
+  </si>
+  <si>
     <t>Bond</t>
   </si>
   <si>
     <t>Commodity</t>
   </si>
   <si>
+    <t>000660.KS  Equity</t>
+  </si>
+  <si>
+    <t>000880.KS  Equity</t>
+  </si>
+  <si>
+    <t>001720.KS  Equity</t>
+  </si>
+  <si>
+    <t>004170.KS  Equity</t>
+  </si>
+  <si>
+    <t>005930.KS  Equity</t>
+  </si>
+  <si>
+    <t>009150.KS  Equity</t>
+  </si>
+  <si>
+    <t>010120.KS  Equity</t>
+  </si>
+  <si>
+    <t>010950.KS  Equity</t>
+  </si>
+  <si>
+    <t>011070.KS  Equity</t>
+  </si>
+  <si>
+    <t>011200  Equity</t>
+  </si>
+  <si>
+    <t>018260.KS  Equity</t>
+  </si>
+  <si>
+    <t>026960.KS  Equity</t>
+  </si>
+  <si>
+    <t>071050  Equity</t>
+  </si>
+  <si>
+    <t>078930.KS  Equity</t>
+  </si>
+  <si>
+    <t>086280  Equity</t>
+  </si>
+  <si>
+    <t>096770.KS  Equity</t>
+  </si>
+  <si>
+    <t>1102  Equity</t>
+  </si>
+  <si>
     <t>1109 HK Equity</t>
   </si>
   <si>
@@ -352,21 +592,42 @@
     <t>1810 HK Equity</t>
   </si>
   <si>
+    <t>2303  Equity</t>
+  </si>
+  <si>
     <t>2359 HK Equity</t>
   </si>
   <si>
+    <t>2408  Equity</t>
+  </si>
+  <si>
+    <t>2412  Equity</t>
+  </si>
+  <si>
     <t>2800 HK Equity</t>
   </si>
   <si>
     <t>2828 HK Equity</t>
   </si>
   <si>
+    <t>2892  Equity</t>
+  </si>
+  <si>
     <t>2899 HK Equity</t>
   </si>
   <si>
     <t>3067 HK Equity</t>
   </si>
   <si>
+    <t>316140.KS  Equity</t>
+  </si>
+  <si>
+    <t>3328 HK Equity</t>
+  </si>
+  <si>
+    <t>3711  Equity</t>
+  </si>
+  <si>
     <t>3750 HK Equity</t>
   </si>
   <si>
@@ -376,6 +637,9 @@
     <t>3988 HK Equity</t>
   </si>
   <si>
+    <t>4062.T JP Equity</t>
+  </si>
+  <si>
     <t>6301.T JP Equity</t>
   </si>
   <si>
@@ -385,15 +649,30 @@
     <t>700 HK Equity</t>
   </si>
   <si>
+    <t>836 HK Equity</t>
+  </si>
+  <si>
     <t>8360.T JP Equity</t>
   </si>
   <si>
     <t>9633 HK Equity</t>
   </si>
   <si>
+    <t>992 HK Equity</t>
+  </si>
+  <si>
     <t>A17U SP Equity</t>
   </si>
   <si>
+    <t>ABBV US Equity</t>
+  </si>
+  <si>
+    <t>AMD US Equity</t>
+  </si>
+  <si>
+    <t>APP US Equity</t>
+  </si>
+  <si>
     <t>AVDV US Equity</t>
   </si>
   <si>
@@ -445,12 +724,18 @@
     <t>D05 SP Equity</t>
   </si>
   <si>
+    <t>DB1 GY Equity</t>
+  </si>
+  <si>
     <t>DBMF US Equity</t>
   </si>
   <si>
     <t>DDOG US Equity</t>
   </si>
   <si>
+    <t>DELL US Equity</t>
+  </si>
+  <si>
     <t>DG US Equity</t>
   </si>
   <si>
@@ -466,6 +751,9 @@
     <t>EWY US Equity</t>
   </si>
   <si>
+    <t>G1A GY Equity</t>
+  </si>
+  <si>
     <t>GEV US Equity</t>
   </si>
   <si>
@@ -481,6 +769,12 @@
     <t>ICE US Equity</t>
   </si>
   <si>
+    <t>IGV US Equity</t>
+  </si>
+  <si>
+    <t>INTC US Equity</t>
+  </si>
+  <si>
     <t>IQQ US Equity</t>
   </si>
   <si>
@@ -493,21 +787,42 @@
     <t>KMLM US Equity</t>
   </si>
   <si>
+    <t>KNIN  Equity</t>
+  </si>
+  <si>
     <t>KORU US Equity</t>
   </si>
   <si>
     <t>LAC US Equity</t>
   </si>
   <si>
+    <t>LIN US Equity</t>
+  </si>
+  <si>
+    <t>LITE US Equity</t>
+  </si>
+  <si>
     <t>LLY US Equity</t>
   </si>
   <si>
+    <t>MAR US Equity</t>
+  </si>
+  <si>
     <t>MCD US Equity</t>
   </si>
   <si>
     <t>ME8U SP Equity</t>
   </si>
   <si>
+    <t>MRK US Equity</t>
+  </si>
+  <si>
+    <t>MRVL US Equity</t>
+  </si>
+  <si>
+    <t>MU US Equity</t>
+  </si>
+  <si>
     <t>NVO US Equity</t>
   </si>
   <si>
@@ -520,12 +835,18 @@
     <t>PKB US Equity</t>
   </si>
   <si>
+    <t>QIA GY Equity</t>
+  </si>
+  <si>
     <t>QQQ US Equity</t>
   </si>
   <si>
     <t>QQQM US Equity</t>
   </si>
   <si>
+    <t>S63 SP Equity</t>
+  </si>
+  <si>
     <t>S68 SP Equity</t>
   </si>
   <si>
@@ -535,6 +856,9 @@
     <t>SCJ US Equity</t>
   </si>
   <si>
+    <t>SHELl LN Equity</t>
+  </si>
+  <si>
     <t>SHLD US Equity</t>
   </si>
   <si>
@@ -547,6 +871,9 @@
     <t>SMH US Equity</t>
   </si>
   <si>
+    <t>SOON  Equity</t>
+  </si>
+  <si>
     <t>SOXX US Equity</t>
   </si>
   <si>
@@ -556,15 +883,30 @@
     <t>SPXL US Equity</t>
   </si>
   <si>
+    <t>STX US Equity</t>
+  </si>
+  <si>
+    <t>TER US Equity</t>
+  </si>
+  <si>
     <t>TQQQ US Equity</t>
   </si>
   <si>
+    <t>TSEM US Equity</t>
+  </si>
+  <si>
+    <t>TTD US Equity</t>
+  </si>
+  <si>
     <t>U11 SP Equity</t>
   </si>
   <si>
     <t>U96 SP Equity</t>
   </si>
   <si>
+    <t>UAE US Equity</t>
+  </si>
+  <si>
     <t>USMV US Equity</t>
   </si>
   <si>
@@ -586,7 +928,16 @@
     <t>VZ US Equity</t>
   </si>
   <si>
+    <t>WDC US Equity</t>
+  </si>
+  <si>
+    <t>XLK US Equity</t>
+  </si>
+  <si>
     <t>XLV US Equity</t>
+  </si>
+  <si>
+    <t>XRO  Equity</t>
   </si>
   <si>
     <t>Z74 SP Equity</t>
@@ -947,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -975,19 +1326,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -995,19 +1346,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1015,19 +1366,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1035,19 +1386,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1055,19 +1406,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F6" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1075,19 +1426,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1095,19 +1446,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1115,19 +1466,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F9" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1135,19 +1486,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1155,19 +1506,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1175,19 +1526,16 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1195,19 +1543,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1215,19 +1563,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1235,19 +1583,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1255,19 +1603,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1275,19 +1623,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1295,19 +1643,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1315,19 +1663,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1335,19 +1683,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1355,19 +1703,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1375,19 +1723,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F22" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1395,19 +1743,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1415,19 +1763,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1435,19 +1783,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F25" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1455,19 +1803,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1475,19 +1823,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1495,19 +1843,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1515,19 +1863,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1535,19 +1883,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F30" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1555,19 +1903,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1575,19 +1923,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1595,19 +1943,19 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1615,19 +1963,19 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1635,19 +1983,19 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F35" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1655,19 +2003,19 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F36" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1675,19 +2023,19 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F37" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1695,19 +2043,19 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F38" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1715,19 +2063,19 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1735,19 +2083,19 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1755,19 +2103,19 @@
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F41" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1775,19 +2123,19 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F42" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1795,19 +2143,19 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F43" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1815,19 +2163,19 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1835,19 +2183,19 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F45" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1855,19 +2203,19 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F46" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1875,19 +2223,19 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F47" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1895,19 +2243,19 @@
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F48" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1915,19 +2263,19 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F49" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1935,19 +2283,19 @@
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F50" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1955,19 +2303,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F51" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1975,19 +2323,19 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1995,19 +2343,19 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F53" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2015,19 +2363,19 @@
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F54" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2035,19 +2383,19 @@
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E55" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2055,19 +2403,19 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="E56" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F56" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2075,19 +2423,19 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D57" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2095,19 +2443,19 @@
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F58" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2115,19 +2463,19 @@
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F59" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2135,19 +2483,19 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F60" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2155,19 +2503,19 @@
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="E61" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F61" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2175,19 +2523,19 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F62" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2195,19 +2543,19 @@
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E63" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F63" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2215,19 +2563,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D64" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2235,19 +2583,19 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F65" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2255,19 +2603,19 @@
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F66" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2275,19 +2623,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F67" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2295,19 +2643,19 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F68" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2315,19 +2663,19 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F69" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2335,19 +2683,19 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="F70" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2355,19 +2703,19 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E71" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2375,19 +2723,19 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D72" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F72" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2395,19 +2743,19 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F73" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2415,19 +2763,19 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F74" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2435,19 +2783,19 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E75" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F75" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2455,19 +2803,19 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E76" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F76" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2475,19 +2823,19 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F77" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2495,19 +2843,19 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E78" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F78" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2515,19 +2863,19 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F79" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2535,19 +2883,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D80" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2555,19 +2903,19 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D81" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E81" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2575,19 +2923,19 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D82" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E82" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2595,19 +2943,19 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D83" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E83" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F83" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2615,19 +2963,19 @@
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="E84" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F84" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2635,19 +2983,19 @@
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D85" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F85" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2655,19 +3003,19 @@
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D86" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F86" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2675,19 +3023,1119 @@
         <v>91</v>
       </c>
       <c r="B87" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" t="s">
+        <v>157</v>
+      </c>
+      <c r="D87" t="s">
+        <v>160</v>
+      </c>
+      <c r="E87" t="s">
+        <v>165</v>
+      </c>
+      <c r="F87" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" t="s">
+        <v>152</v>
+      </c>
+      <c r="C88" t="s">
+        <v>157</v>
+      </c>
+      <c r="D88" t="s">
+        <v>159</v>
+      </c>
+      <c r="E88" t="s">
+        <v>165</v>
+      </c>
+      <c r="F88" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" t="s">
+        <v>151</v>
+      </c>
+      <c r="C89" t="s">
+        <v>157</v>
+      </c>
+      <c r="D89" t="s">
+        <v>161</v>
+      </c>
+      <c r="E89" t="s">
+        <v>165</v>
+      </c>
+      <c r="F89" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
         <v>94</v>
       </c>
-      <c r="C87" t="s">
+      <c r="B90" t="s">
+        <v>152</v>
+      </c>
+      <c r="C90" t="s">
+        <v>157</v>
+      </c>
+      <c r="D90" t="s">
+        <v>160</v>
+      </c>
+      <c r="E90" t="s">
+        <v>165</v>
+      </c>
+      <c r="F90" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" t="s">
+        <v>157</v>
+      </c>
+      <c r="D91" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" t="s">
+        <v>165</v>
+      </c>
+      <c r="F91" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
         <v>96</v>
       </c>
-      <c r="D87" t="s">
+      <c r="B92" t="s">
+        <v>152</v>
+      </c>
+      <c r="C92" t="s">
+        <v>157</v>
+      </c>
+      <c r="D92" t="s">
+        <v>160</v>
+      </c>
+      <c r="E92" t="s">
+        <v>165</v>
+      </c>
+      <c r="F92" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
         <v>97</v>
       </c>
-      <c r="E87" t="s">
+      <c r="B93" t="s">
+        <v>152</v>
+      </c>
+      <c r="C93" t="s">
+        <v>157</v>
+      </c>
+      <c r="D93" t="s">
+        <v>159</v>
+      </c>
+      <c r="E93" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" t="s">
+        <v>152</v>
+      </c>
+      <c r="C94" t="s">
+        <v>157</v>
+      </c>
+      <c r="D94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E94" t="s">
+        <v>165</v>
+      </c>
+      <c r="F94" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" t="s">
+        <v>157</v>
+      </c>
+      <c r="D95" t="s">
+        <v>159</v>
+      </c>
+      <c r="E95" t="s">
+        <v>165</v>
+      </c>
+      <c r="F95" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96" t="s">
+        <v>159</v>
+      </c>
+      <c r="E96" t="s">
+        <v>165</v>
+      </c>
+      <c r="F96" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" t="s">
+        <v>152</v>
+      </c>
+      <c r="C97" t="s">
+        <v>157</v>
+      </c>
+      <c r="D97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E97" t="s">
+        <v>165</v>
+      </c>
+      <c r="F97" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" t="s">
+        <v>152</v>
+      </c>
+      <c r="C98" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" t="s">
+        <v>159</v>
+      </c>
+      <c r="E98" t="s">
+        <v>165</v>
+      </c>
+      <c r="F98" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
         <v>103</v>
       </c>
-      <c r="F87" t="s">
-        <v>191</v>
+      <c r="B99" t="s">
+        <v>151</v>
+      </c>
+      <c r="C99" t="s">
+        <v>157</v>
+      </c>
+      <c r="D99" t="s">
+        <v>161</v>
+      </c>
+      <c r="E99" t="s">
+        <v>165</v>
+      </c>
+      <c r="F99" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" t="s">
+        <v>152</v>
+      </c>
+      <c r="C100" t="s">
+        <v>157</v>
+      </c>
+      <c r="D100" t="s">
+        <v>159</v>
+      </c>
+      <c r="E100" t="s">
+        <v>165</v>
+      </c>
+      <c r="F100" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" t="s">
+        <v>157</v>
+      </c>
+      <c r="D101" t="s">
+        <v>159</v>
+      </c>
+      <c r="E101" t="s">
+        <v>165</v>
+      </c>
+      <c r="F101" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" t="s">
+        <v>152</v>
+      </c>
+      <c r="C102" t="s">
+        <v>157</v>
+      </c>
+      <c r="D102" t="s">
+        <v>159</v>
+      </c>
+      <c r="E102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F102" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" t="s">
+        <v>152</v>
+      </c>
+      <c r="C103" t="s">
+        <v>157</v>
+      </c>
+      <c r="D103" t="s">
+        <v>159</v>
+      </c>
+      <c r="E103" t="s">
+        <v>165</v>
+      </c>
+      <c r="F103" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104" t="s">
+        <v>152</v>
+      </c>
+      <c r="C104" t="s">
+        <v>157</v>
+      </c>
+      <c r="D104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E104" t="s">
+        <v>165</v>
+      </c>
+      <c r="F104" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>109</v>
+      </c>
+      <c r="B105" t="s">
+        <v>152</v>
+      </c>
+      <c r="C105" t="s">
+        <v>157</v>
+      </c>
+      <c r="D105" t="s">
+        <v>159</v>
+      </c>
+      <c r="E105" t="s">
+        <v>165</v>
+      </c>
+      <c r="F105" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>110</v>
+      </c>
+      <c r="B106" t="s">
+        <v>152</v>
+      </c>
+      <c r="C106" t="s">
+        <v>157</v>
+      </c>
+      <c r="D106" t="s">
+        <v>160</v>
+      </c>
+      <c r="E106" t="s">
+        <v>165</v>
+      </c>
+      <c r="F106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107" t="s">
+        <v>153</v>
+      </c>
+      <c r="C107" t="s">
+        <v>157</v>
+      </c>
+      <c r="D107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E107" t="s">
+        <v>165</v>
+      </c>
+      <c r="F107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" t="s">
+        <v>157</v>
+      </c>
+      <c r="D108" t="s">
+        <v>160</v>
+      </c>
+      <c r="E108" t="s">
+        <v>165</v>
+      </c>
+      <c r="F108" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109" t="s">
+        <v>152</v>
+      </c>
+      <c r="C109" t="s">
+        <v>157</v>
+      </c>
+      <c r="D109" t="s">
+        <v>160</v>
+      </c>
+      <c r="E109" t="s">
+        <v>165</v>
+      </c>
+      <c r="F109" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" t="s">
+        <v>151</v>
+      </c>
+      <c r="C110" t="s">
+        <v>157</v>
+      </c>
+      <c r="D110" t="s">
+        <v>159</v>
+      </c>
+      <c r="E110" t="s">
+        <v>165</v>
+      </c>
+      <c r="F110" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" t="s">
+        <v>151</v>
+      </c>
+      <c r="C111" t="s">
+        <v>157</v>
+      </c>
+      <c r="D111" t="s">
+        <v>159</v>
+      </c>
+      <c r="E111" t="s">
+        <v>165</v>
+      </c>
+      <c r="F111" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>116</v>
+      </c>
+      <c r="B112" t="s">
+        <v>152</v>
+      </c>
+      <c r="C112" t="s">
+        <v>157</v>
+      </c>
+      <c r="D112" t="s">
+        <v>160</v>
+      </c>
+      <c r="E112" t="s">
+        <v>165</v>
+      </c>
+      <c r="F112" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>117</v>
+      </c>
+      <c r="B113" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" t="s">
+        <v>157</v>
+      </c>
+      <c r="D113" t="s">
+        <v>160</v>
+      </c>
+      <c r="E113" t="s">
+        <v>165</v>
+      </c>
+      <c r="F113" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>118</v>
+      </c>
+      <c r="B114" t="s">
+        <v>155</v>
+      </c>
+      <c r="C114" t="s">
+        <v>157</v>
+      </c>
+      <c r="D114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E114" t="s">
+        <v>165</v>
+      </c>
+      <c r="F114" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" t="s">
+        <v>152</v>
+      </c>
+      <c r="C115" t="s">
+        <v>157</v>
+      </c>
+      <c r="D115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E115" t="s">
+        <v>165</v>
+      </c>
+      <c r="F115" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" t="s">
+        <v>152</v>
+      </c>
+      <c r="C116" t="s">
+        <v>157</v>
+      </c>
+      <c r="D116" t="s">
+        <v>163</v>
+      </c>
+      <c r="E116" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C117" t="s">
+        <v>157</v>
+      </c>
+      <c r="D117" t="s">
+        <v>159</v>
+      </c>
+      <c r="E117" t="s">
+        <v>165</v>
+      </c>
+      <c r="F117" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>122</v>
+      </c>
+      <c r="B118" t="s">
+        <v>152</v>
+      </c>
+      <c r="C118" t="s">
+        <v>157</v>
+      </c>
+      <c r="D118" t="s">
+        <v>160</v>
+      </c>
+      <c r="E118" t="s">
+        <v>165</v>
+      </c>
+      <c r="F118" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>123</v>
+      </c>
+      <c r="B119" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" t="s">
+        <v>157</v>
+      </c>
+      <c r="D119" t="s">
+        <v>159</v>
+      </c>
+      <c r="E119" t="s">
+        <v>165</v>
+      </c>
+      <c r="F119" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>124</v>
+      </c>
+      <c r="B120" t="s">
+        <v>152</v>
+      </c>
+      <c r="C120" t="s">
+        <v>157</v>
+      </c>
+      <c r="D120" t="s">
+        <v>160</v>
+      </c>
+      <c r="E120" t="s">
+        <v>165</v>
+      </c>
+      <c r="F120" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" t="s">
+        <v>152</v>
+      </c>
+      <c r="C121" t="s">
+        <v>157</v>
+      </c>
+      <c r="D121" t="s">
+        <v>160</v>
+      </c>
+      <c r="E121" t="s">
+        <v>165</v>
+      </c>
+      <c r="F121" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>126</v>
+      </c>
+      <c r="B122" t="s">
+        <v>152</v>
+      </c>
+      <c r="C122" t="s">
+        <v>157</v>
+      </c>
+      <c r="D122" t="s">
+        <v>160</v>
+      </c>
+      <c r="E122" t="s">
+        <v>165</v>
+      </c>
+      <c r="F122" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>127</v>
+      </c>
+      <c r="B123" t="s">
+        <v>152</v>
+      </c>
+      <c r="C123" t="s">
+        <v>157</v>
+      </c>
+      <c r="D123" t="s">
+        <v>159</v>
+      </c>
+      <c r="E123" t="s">
+        <v>165</v>
+      </c>
+      <c r="F123" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>128</v>
+      </c>
+      <c r="B124" t="s">
+        <v>152</v>
+      </c>
+      <c r="C124" t="s">
+        <v>157</v>
+      </c>
+      <c r="D124" t="s">
+        <v>159</v>
+      </c>
+      <c r="E124" t="s">
+        <v>165</v>
+      </c>
+      <c r="F124" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125" t="s">
+        <v>152</v>
+      </c>
+      <c r="C125" t="s">
+        <v>157</v>
+      </c>
+      <c r="D125" t="s">
+        <v>160</v>
+      </c>
+      <c r="E125" t="s">
+        <v>165</v>
+      </c>
+      <c r="F125" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126" t="s">
+        <v>152</v>
+      </c>
+      <c r="C126" t="s">
+        <v>157</v>
+      </c>
+      <c r="D126" t="s">
+        <v>159</v>
+      </c>
+      <c r="E126" t="s">
+        <v>165</v>
+      </c>
+      <c r="F126" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127" t="s">
+        <v>152</v>
+      </c>
+      <c r="C127" t="s">
+        <v>157</v>
+      </c>
+      <c r="D127" t="s">
+        <v>159</v>
+      </c>
+      <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>132</v>
+      </c>
+      <c r="B128" t="s">
+        <v>151</v>
+      </c>
+      <c r="C128" t="s">
+        <v>157</v>
+      </c>
+      <c r="D128" t="s">
+        <v>159</v>
+      </c>
+      <c r="E128" t="s">
+        <v>165</v>
+      </c>
+      <c r="F128" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>133</v>
+      </c>
+      <c r="B129" t="s">
+        <v>151</v>
+      </c>
+      <c r="C129" t="s">
+        <v>157</v>
+      </c>
+      <c r="D129" t="s">
+        <v>159</v>
+      </c>
+      <c r="E129" t="s">
+        <v>165</v>
+      </c>
+      <c r="F129" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>134</v>
+      </c>
+      <c r="B130" t="s">
+        <v>152</v>
+      </c>
+      <c r="C130" t="s">
+        <v>157</v>
+      </c>
+      <c r="D130" t="s">
+        <v>160</v>
+      </c>
+      <c r="E130" t="s">
+        <v>165</v>
+      </c>
+      <c r="F130" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>135</v>
+      </c>
+      <c r="B131" t="s">
+        <v>152</v>
+      </c>
+      <c r="C131" t="s">
+        <v>157</v>
+      </c>
+      <c r="D131" t="s">
+        <v>160</v>
+      </c>
+      <c r="E131" t="s">
+        <v>165</v>
+      </c>
+      <c r="F131" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132" t="s">
+        <v>152</v>
+      </c>
+      <c r="C132" t="s">
+        <v>157</v>
+      </c>
+      <c r="D132" t="s">
+        <v>164</v>
+      </c>
+      <c r="E132" t="s">
+        <v>168</v>
+      </c>
+      <c r="F132" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>137</v>
+      </c>
+      <c r="B133" t="s">
+        <v>152</v>
+      </c>
+      <c r="C133" t="s">
+        <v>157</v>
+      </c>
+      <c r="D133" t="s">
+        <v>160</v>
+      </c>
+      <c r="E133" t="s">
+        <v>165</v>
+      </c>
+      <c r="F133" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>138</v>
+      </c>
+      <c r="B134" t="s">
+        <v>152</v>
+      </c>
+      <c r="C134" t="s">
+        <v>157</v>
+      </c>
+      <c r="D134" t="s">
+        <v>160</v>
+      </c>
+      <c r="E134" t="s">
+        <v>165</v>
+      </c>
+      <c r="F134" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" t="s">
+        <v>152</v>
+      </c>
+      <c r="C135" t="s">
+        <v>157</v>
+      </c>
+      <c r="D135" t="s">
+        <v>159</v>
+      </c>
+      <c r="E135" t="s">
+        <v>165</v>
+      </c>
+      <c r="F135" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>140</v>
+      </c>
+      <c r="B136" t="s">
+        <v>152</v>
+      </c>
+      <c r="C136" t="s">
+        <v>157</v>
+      </c>
+      <c r="D136" t="s">
+        <v>159</v>
+      </c>
+      <c r="E136" t="s">
+        <v>165</v>
+      </c>
+      <c r="F136" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" t="s">
+        <v>152</v>
+      </c>
+      <c r="C137" t="s">
+        <v>157</v>
+      </c>
+      <c r="D137" t="s">
+        <v>159</v>
+      </c>
+      <c r="E137" t="s">
+        <v>165</v>
+      </c>
+      <c r="F137" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>142</v>
+      </c>
+      <c r="B138" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138" t="s">
+        <v>157</v>
+      </c>
+      <c r="D138" t="s">
+        <v>159</v>
+      </c>
+      <c r="E138" t="s">
+        <v>165</v>
+      </c>
+      <c r="F138" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>143</v>
+      </c>
+      <c r="B139" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139" t="s">
+        <v>157</v>
+      </c>
+      <c r="D139" t="s">
+        <v>160</v>
+      </c>
+      <c r="E139" t="s">
+        <v>165</v>
+      </c>
+      <c r="F139" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" t="s">
+        <v>152</v>
+      </c>
+      <c r="C140" t="s">
+        <v>157</v>
+      </c>
+      <c r="D140" t="s">
+        <v>160</v>
+      </c>
+      <c r="E140" t="s">
+        <v>165</v>
+      </c>
+      <c r="F140" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>145</v>
+      </c>
+      <c r="B141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C141" t="s">
+        <v>157</v>
+      </c>
+      <c r="D141" t="s">
+        <v>159</v>
+      </c>
+      <c r="E141" t="s">
+        <v>165</v>
+      </c>
+      <c r="F141" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" t="s">
+        <v>151</v>
+      </c>
+      <c r="C142" t="s">
+        <v>157</v>
+      </c>
+      <c r="D142" t="s">
+        <v>159</v>
+      </c>
+      <c r="E142" t="s">
+        <v>165</v>
+      </c>
+      <c r="F142" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
